--- a/DateBase/orders/Nhat 48_2026-4-2.xlsx
+++ b/DateBase/orders/Nhat 48_2026-4-2.xlsx
@@ -517,6 +517,9 @@
       <c r="C11" t="str">
         <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -575,7 +578,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>055540553535350</v>
+        <v>055540553535355</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-4-2.xlsx
+++ b/DateBase/orders/Nhat 48_2026-4-2.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -521,9 +521,95 @@
         <v>5</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>439_九星叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>4</v>
+      </c>
+      <c r="C13" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5</v>
+      </c>
+      <c r="C15" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>157_流沙_Quicksand_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>6</v>
+      </c>
+      <c r="C20" t="str">
+        <v>157_流沙_Quicksand_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -578,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>055540553535355</v>
+        <v>055540553535355841104571010200</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-4-2.xlsx
+++ b/DateBase/orders/Nhat 48_2026-4-2.xlsx
@@ -606,6 +606,9 @@
       <c r="C21" t="str">
         <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -664,7 +667,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>055540553535355841104571010200</v>
+        <v>0555405535353558411045710102014</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-4-2.xlsx
+++ b/DateBase/orders/Nhat 48_2026-4-2.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -610,9 +610,92 @@
         <v>14</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F22" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>7</v>
+      </c>
+      <c r="C23" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>820_蝴蝶洋牡丹粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>753_蝴蝶洋牡丹黄_butterfly  Ranunculus_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>493_咖喱花_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>8</v>
+      </c>
+      <c r="C27" t="str">
+        <v>662_大丽花 白_undefined_undefined_5stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>648_洋牡丹河内_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>788_直葱_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>500_千鸟飞燕 粉_larkspur pink_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>503_丁香花 粉_lilac pink_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -667,7 +750,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0555405535353558411045710102014</v>
+        <v>0555405535353558411045710102014152056151555100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-4-2.xlsx
+++ b/DateBase/orders/Nhat 48_2026-4-2.xlsx
@@ -692,6 +692,9 @@
       <c r="C31" t="str">
         <v>503_丁香花 粉_lilac pink_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -750,7 +753,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0555405535353558411045710102014152056151555100</v>
+        <v>0555405535353558411045710102014152056151555105</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-4-2.xlsx
+++ b/DateBase/orders/Nhat 48_2026-4-2.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -696,9 +696,95 @@
         <v>5</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>526_大刺秦_Eryngium_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>871_洋牡丹高山雪_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F33" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>9</v>
+      </c>
+      <c r="C34" t="str">
+        <v>452_粉吊鸟_pink hanging heliconia_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>10</v>
+      </c>
+      <c r="C35" t="str">
+        <v>370_水腊叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>11</v>
+      </c>
+      <c r="C36" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F36" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F37" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>630_吸色康乃馨天蓝_tinted tiffany blue_undefined_20stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>255_九星蓝狐_Ocean Song spray_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>71_霜雪mini_Snowy_Gerbera L._20stems</v>
+      </c>
+      <c r="F40" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>80_冰清玉洁_undefined_Gerbera L._20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -753,7 +839,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0555405535353558411045710102014152056151555105</v>
+        <v>055540553535355841104571010201415205615155510555121021867150</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-4-2.xlsx
+++ b/DateBase/orders/Nhat 48_2026-4-2.xlsx
@@ -781,6 +781,9 @@
       <c r="C41" t="str">
         <v>80_冰清玉洁_undefined_Gerbera L._20stems</v>
       </c>
+      <c r="F41" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -839,7 +842,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>055540553535355841104571010201415205615155510555121021867150</v>
+        <v>055540553535355841104571010201415205615155510555121021867155</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-4-2.xlsx
+++ b/DateBase/orders/Nhat 48_2026-4-2.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L42"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -785,9 +785,20 @@
         <v>5</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>12</v>
+      </c>
+      <c r="C42" t="str">
+        <v>636_干花大叶白_undefined_undefined_1stem</v>
+      </c>
+      <c r="F42" t="str">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L42"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -842,7 +853,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>055540553535355841104571010201415205615155510555121021867155</v>
+        <v>05554055353535584110457101020141520561515551055512102186715512</v>
       </c>
     </row>
   </sheetData>
